--- a/artfynd/A 11880-2025 artfynd.xlsx
+++ b/artfynd/A 11880-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,51 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125123712</v>
+        <v>136952975</v>
       </c>
       <c r="B2" t="n">
-        <v>80432</v>
+        <v>91889</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bergtjärnen, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346722</v>
+        <v>346697</v>
       </c>
       <c r="R2" t="n">
-        <v>6601668</v>
+        <v>6601777</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,17 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Noterad på fyra ganska klena aspar.</t>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -767,31 +769,1288 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Rees</t>
+          <t>Jesper Granback</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136952975</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136952979</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91889</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>346671</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6601733</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Silbodal</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:28</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136952979</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125123712</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>346722</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6601668</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Silbodal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-08</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Noterad på fyra ganska klena aspar.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jan Rees</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/125123712</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136952949</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80591</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>346815</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6601639</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Silbodal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136952949</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136952967</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80591</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>346734</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6601682</v>
+      </c>
+      <c r="S6" t="n">
+        <v>6</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Silbodal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136952967</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136952968</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80591</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>346742</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6601679</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Silbodal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136952968</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136952969</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80591</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>346738</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6601685</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Silbodal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136952969</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136952972</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80591</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>346739</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6601690</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Silbodal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136952972</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136952973</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80591</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>346744</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6601694</v>
+      </c>
+      <c r="S10" t="n">
+        <v>7</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Silbodal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136952973</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136952964</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>346747</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6601647</v>
+      </c>
+      <c r="S11" t="n">
+        <v>8</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Silbodal</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136952964</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136952941</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>346849</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6601688</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Silbodal</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136952941</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136953284</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80541</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bergtjärnen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>346738</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6601685</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Årjäng</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Silbodal</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jesper Granback</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136953284</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11880-2025 artfynd.xlsx
+++ b/artfynd/A 11880-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952975</v>
       </c>
       <c r="B2" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136952979</v>
       </c>
       <c r="B3" t="n">
-        <v>91889</v>
+        <v>91891</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136952949</v>
       </c>
       <c r="B5" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136952967</v>
       </c>
       <c r="B6" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>346734</v>
       </c>
       <c r="R6" t="n">
-        <v>6601682</v>
+        <v>6601683</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
@@ -1242,7 +1242,7 @@
         <v>136952968</v>
       </c>
       <c r="B7" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136952969</v>
       </c>
       <c r="B8" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>136952972</v>
       </c>
       <c r="B9" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136952973</v>
       </c>
       <c r="B10" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>136953284</v>
       </c>
       <c r="B13" t="n">
-        <v>80541</v>
+        <v>80545</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11880-2025 artfynd.xlsx
+++ b/artfynd/A 11880-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952975</v>
       </c>
       <c r="B2" t="n">
-        <v>91891</v>
+        <v>91893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136952979</v>
       </c>
       <c r="B3" t="n">
-        <v>91891</v>
+        <v>91893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136952949</v>
       </c>
       <c r="B5" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136952967</v>
       </c>
       <c r="B6" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>136952968</v>
       </c>
       <c r="B7" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136952969</v>
       </c>
       <c r="B8" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>136952972</v>
       </c>
       <c r="B9" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136952973</v>
       </c>
       <c r="B10" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>136953284</v>
       </c>
       <c r="B13" t="n">
-        <v>80545</v>
+        <v>80547</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11880-2025 artfynd.xlsx
+++ b/artfynd/A 11880-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952975</v>
       </c>
       <c r="B2" t="n">
-        <v>91893</v>
+        <v>91894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136952979</v>
       </c>
       <c r="B3" t="n">
-        <v>91893</v>
+        <v>91894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136952949</v>
       </c>
       <c r="B5" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136952967</v>
       </c>
       <c r="B6" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>346734</v>
       </c>
       <c r="R6" t="n">
-        <v>6601683</v>
+        <v>6601682</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
@@ -1242,7 +1242,7 @@
         <v>136952968</v>
       </c>
       <c r="B7" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136952969</v>
       </c>
       <c r="B8" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>136952972</v>
       </c>
       <c r="B9" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136952973</v>
       </c>
       <c r="B10" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>136953284</v>
       </c>
       <c r="B13" t="n">
-        <v>80547</v>
+        <v>80548</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11880-2025 artfynd.xlsx
+++ b/artfynd/A 11880-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952975</v>
       </c>
       <c r="B2" t="n">
-        <v>91894</v>
+        <v>91900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136952979</v>
       </c>
       <c r="B3" t="n">
-        <v>91894</v>
+        <v>91900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11880-2025 artfynd.xlsx
+++ b/artfynd/A 11880-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952975</v>
       </c>
       <c r="B2" t="n">
-        <v>91900</v>
+        <v>91904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136952979</v>
       </c>
       <c r="B3" t="n">
-        <v>91900</v>
+        <v>91904</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136952949</v>
       </c>
       <c r="B5" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136952967</v>
       </c>
       <c r="B6" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>346734</v>
       </c>
       <c r="R6" t="n">
-        <v>6601682</v>
+        <v>6601683</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
@@ -1242,7 +1242,7 @@
         <v>136952968</v>
       </c>
       <c r="B7" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136952969</v>
       </c>
       <c r="B8" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>136952972</v>
       </c>
       <c r="B9" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136952973</v>
       </c>
       <c r="B10" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>136953284</v>
       </c>
       <c r="B13" t="n">
-        <v>80548</v>
+        <v>80550</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11880-2025 artfynd.xlsx
+++ b/artfynd/A 11880-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952975</v>
       </c>
       <c r="B2" t="n">
-        <v>91904</v>
+        <v>91906</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136952979</v>
       </c>
       <c r="B3" t="n">
-        <v>91904</v>
+        <v>91906</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136952949</v>
       </c>
       <c r="B5" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136952967</v>
       </c>
       <c r="B6" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>136952968</v>
       </c>
       <c r="B7" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136952969</v>
       </c>
       <c r="B8" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>136952972</v>
       </c>
       <c r="B9" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136952973</v>
       </c>
       <c r="B10" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>136953284</v>
       </c>
       <c r="B13" t="n">
-        <v>80550</v>
+        <v>80553</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11880-2025 artfynd.xlsx
+++ b/artfynd/A 11880-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952975</v>
       </c>
       <c r="B2" t="n">
-        <v>91906</v>
+        <v>91919</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136952979</v>
       </c>
       <c r="B3" t="n">
-        <v>91906</v>
+        <v>91919</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136952949</v>
       </c>
       <c r="B5" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136952967</v>
       </c>
       <c r="B6" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>136952968</v>
       </c>
       <c r="B7" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136952969</v>
       </c>
       <c r="B8" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>136952972</v>
       </c>
       <c r="B9" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136952973</v>
       </c>
       <c r="B10" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136952964</v>
       </c>
       <c r="B11" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>136953284</v>
       </c>
       <c r="B13" t="n">
-        <v>80553</v>
+        <v>80566</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11880-2025 artfynd.xlsx
+++ b/artfynd/A 11880-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952975</v>
       </c>
       <c r="B2" t="n">
-        <v>91919</v>
+        <v>91921</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136952979</v>
       </c>
       <c r="B3" t="n">
-        <v>91919</v>
+        <v>91921</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136952949</v>
       </c>
       <c r="B5" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136952967</v>
       </c>
       <c r="B6" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>136952968</v>
       </c>
       <c r="B7" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136952969</v>
       </c>
       <c r="B8" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>136952972</v>
       </c>
       <c r="B9" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136952973</v>
       </c>
       <c r="B10" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136952964</v>
       </c>
       <c r="B11" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>136952941</v>
       </c>
       <c r="B12" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
         <v>136953284</v>
       </c>
       <c r="B13" t="n">
-        <v>80566</v>
+        <v>80568</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11880-2025 artfynd.xlsx
+++ b/artfynd/A 11880-2025 artfynd.xlsx
@@ -1722,11 +1722,7 @@
       <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>

--- a/artfynd/A 11880-2025 artfynd.xlsx
+++ b/artfynd/A 11880-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952975</v>
       </c>
       <c r="B2" t="n">
-        <v>91921</v>
+        <v>91924</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136952979</v>
       </c>
       <c r="B3" t="n">
-        <v>91921</v>
+        <v>91924</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>346734</v>
       </c>
       <c r="R6" t="n">
-        <v>6601683</v>
+        <v>6601682</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>

--- a/artfynd/A 11880-2025 artfynd.xlsx
+++ b/artfynd/A 11880-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952975</v>
       </c>
       <c r="B2" t="n">
-        <v>91924</v>
+        <v>91934</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136952979</v>
       </c>
       <c r="B3" t="n">
-        <v>91924</v>
+        <v>91934</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136952949</v>
       </c>
       <c r="B5" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136952967</v>
       </c>
       <c r="B6" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>136952968</v>
       </c>
       <c r="B7" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136952969</v>
       </c>
       <c r="B8" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>136952972</v>
       </c>
       <c r="B9" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136952973</v>
       </c>
       <c r="B10" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136952964</v>
       </c>
       <c r="B11" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1810,7 +1810,7 @@
         <v>136952941</v>
       </c>
       <c r="B12" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>136953284</v>
       </c>
       <c r="B13" t="n">
-        <v>80568</v>
+        <v>80578</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11880-2025 artfynd.xlsx
+++ b/artfynd/A 11880-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952975</v>
       </c>
       <c r="B2" t="n">
-        <v>91934</v>
+        <v>91935</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136952979</v>
       </c>
       <c r="B3" t="n">
-        <v>91934</v>
+        <v>91935</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11880-2025 artfynd.xlsx
+++ b/artfynd/A 11880-2025 artfynd.xlsx
@@ -1165,7 +1165,7 @@
         <v>346734</v>
       </c>
       <c r="R6" t="n">
-        <v>6601682</v>
+        <v>6601683</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>

--- a/artfynd/A 11880-2025 artfynd.xlsx
+++ b/artfynd/A 11880-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952975</v>
       </c>
       <c r="B2" t="n">
-        <v>91935</v>
+        <v>91938</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136952979</v>
       </c>
       <c r="B3" t="n">
-        <v>91935</v>
+        <v>91938</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136952949</v>
       </c>
       <c r="B5" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136952967</v>
       </c>
       <c r="B6" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>346734</v>
       </c>
       <c r="R6" t="n">
-        <v>6601683</v>
+        <v>6601682</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
@@ -1242,7 +1242,7 @@
         <v>136952968</v>
       </c>
       <c r="B7" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136952969</v>
       </c>
       <c r="B8" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>136952972</v>
       </c>
       <c r="B9" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136952973</v>
       </c>
       <c r="B10" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136952964</v>
       </c>
       <c r="B11" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>136953284</v>
       </c>
       <c r="B13" t="n">
-        <v>80578</v>
+        <v>80581</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11880-2025 artfynd.xlsx
+++ b/artfynd/A 11880-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952975</v>
       </c>
       <c r="B2" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136952979</v>
       </c>
       <c r="B3" t="n">
-        <v>91938</v>
+        <v>91940</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 11880-2025 artfynd.xlsx
+++ b/artfynd/A 11880-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952975</v>
       </c>
       <c r="B2" t="n">
-        <v>91940</v>
+        <v>91945</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136952979</v>
       </c>
       <c r="B3" t="n">
-        <v>91940</v>
+        <v>91945</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136952949</v>
       </c>
       <c r="B5" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136952967</v>
       </c>
       <c r="B6" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>136952968</v>
       </c>
       <c r="B7" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136952969</v>
       </c>
       <c r="B8" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>136952972</v>
       </c>
       <c r="B9" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136952973</v>
       </c>
       <c r="B10" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136952964</v>
       </c>
       <c r="B11" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>136953284</v>
       </c>
       <c r="B13" t="n">
-        <v>80581</v>
+        <v>80586</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11880-2025 artfynd.xlsx
+++ b/artfynd/A 11880-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952975</v>
       </c>
       <c r="B2" t="n">
-        <v>91945</v>
+        <v>91957</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136952979</v>
       </c>
       <c r="B3" t="n">
-        <v>91945</v>
+        <v>91957</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136952949</v>
       </c>
       <c r="B5" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136952967</v>
       </c>
       <c r="B6" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>346734</v>
       </c>
       <c r="R6" t="n">
-        <v>6601682</v>
+        <v>6601683</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
@@ -1242,7 +1242,7 @@
         <v>136952968</v>
       </c>
       <c r="B7" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136952969</v>
       </c>
       <c r="B8" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>136952972</v>
       </c>
       <c r="B9" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136952973</v>
       </c>
       <c r="B10" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>136953284</v>
       </c>
       <c r="B13" t="n">
-        <v>80586</v>
+        <v>80597</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11880-2025 artfynd.xlsx
+++ b/artfynd/A 11880-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952975</v>
       </c>
       <c r="B2" t="n">
-        <v>91957</v>
+        <v>91958</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136952979</v>
       </c>
       <c r="B3" t="n">
-        <v>91957</v>
+        <v>91958</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136952949</v>
       </c>
       <c r="B5" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136952967</v>
       </c>
       <c r="B6" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>346734</v>
       </c>
       <c r="R6" t="n">
-        <v>6601683</v>
+        <v>6601682</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
@@ -1242,7 +1242,7 @@
         <v>136952968</v>
       </c>
       <c r="B7" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136952969</v>
       </c>
       <c r="B8" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>136952972</v>
       </c>
       <c r="B9" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136952973</v>
       </c>
       <c r="B10" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>136953284</v>
       </c>
       <c r="B13" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11880-2025 artfynd.xlsx
+++ b/artfynd/A 11880-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952975</v>
       </c>
       <c r="B2" t="n">
-        <v>91958</v>
+        <v>91961</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136952979</v>
       </c>
       <c r="B3" t="n">
-        <v>91958</v>
+        <v>91961</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136952949</v>
       </c>
       <c r="B5" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136952967</v>
       </c>
       <c r="B6" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>346734</v>
       </c>
       <c r="R6" t="n">
-        <v>6601682</v>
+        <v>6601683</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
@@ -1242,7 +1242,7 @@
         <v>136952968</v>
       </c>
       <c r="B7" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136952969</v>
       </c>
       <c r="B8" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>136952972</v>
       </c>
       <c r="B9" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136952973</v>
       </c>
       <c r="B10" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>136953284</v>
       </c>
       <c r="B13" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11880-2025 artfynd.xlsx
+++ b/artfynd/A 11880-2025 artfynd.xlsx
@@ -1165,7 +1165,7 @@
         <v>346734</v>
       </c>
       <c r="R6" t="n">
-        <v>6601683</v>
+        <v>6601682</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>

--- a/artfynd/A 11880-2025 artfynd.xlsx
+++ b/artfynd/A 11880-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952975</v>
       </c>
       <c r="B2" t="n">
-        <v>91961</v>
+        <v>91962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136952979</v>
       </c>
       <c r="B3" t="n">
-        <v>91961</v>
+        <v>91962</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136952949</v>
       </c>
       <c r="B5" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136952967</v>
       </c>
       <c r="B6" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>346734</v>
       </c>
       <c r="R6" t="n">
-        <v>6601682</v>
+        <v>6601683</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
@@ -1242,7 +1242,7 @@
         <v>136952968</v>
       </c>
       <c r="B7" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136952969</v>
       </c>
       <c r="B8" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>136952972</v>
       </c>
       <c r="B9" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136952973</v>
       </c>
       <c r="B10" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>136953284</v>
       </c>
       <c r="B13" t="n">
-        <v>80600</v>
+        <v>80601</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 11880-2025 artfynd.xlsx
+++ b/artfynd/A 11880-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136952975</v>
       </c>
       <c r="B2" t="n">
-        <v>91962</v>
+        <v>91965</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136952979</v>
       </c>
       <c r="B3" t="n">
-        <v>91962</v>
+        <v>91965</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>136952949</v>
       </c>
       <c r="B5" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1130,7 +1130,7 @@
         <v>136952967</v>
       </c>
       <c r="B6" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,7 +1165,7 @@
         <v>346734</v>
       </c>
       <c r="R6" t="n">
-        <v>6601683</v>
+        <v>6601682</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
@@ -1242,7 +1242,7 @@
         <v>136952968</v>
       </c>
       <c r="B7" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>136952969</v>
       </c>
       <c r="B8" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>136952972</v>
       </c>
       <c r="B9" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>136952973</v>
       </c>
       <c r="B10" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>136952964</v>
       </c>
       <c r="B11" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1922,7 +1922,7 @@
         <v>136953284</v>
       </c>
       <c r="B13" t="n">
-        <v>80601</v>
+        <v>80604</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
